--- a/public/data_karyawan.xlsx
+++ b/public/data_karyawan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fairuz\Desktop\laragon\www\landing-page-wo - Copy\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fairuz\Desktop\laragon\www\jembo-project\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134D62C9-50F5-49CC-94AE-15F36D1BF684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE2EFB4-A4B5-42ED-885F-E00CAE00CD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20930" uniqueCount="2337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20930" uniqueCount="2339">
   <si>
     <t>Employee ID</t>
   </si>
@@ -7041,6 +7041,12 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>nik</t>
+  </si>
+  <si>
+    <t>name</t>
   </si>
 </sst>
 </file>
@@ -27042,7 +27048,7 @@
   <dimension ref="A1:F982"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.140625" customWidth="1"/>
@@ -27052,10 +27058,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2337</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2338</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
